--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/9.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/9.xlsx
@@ -426,13 +426,13 @@
         <v>-20.36743814980577</v>
       </c>
       <c r="E2">
-        <v>-17.83986655976287</v>
+        <v>-16.46548375538294</v>
       </c>
       <c r="F2">
-        <v>-1.495002016021735</v>
+        <v>-0.9197969453962032</v>
       </c>
       <c r="G2">
-        <v>-10.36808152626775</v>
+        <v>-6.557100183607571</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.91738123126412</v>
       </c>
       <c r="E3">
-        <v>-18.29473365993733</v>
+        <v>-15.80981958923437</v>
       </c>
       <c r="F3">
-        <v>-1.689245059936788</v>
+        <v>-1.310169225802484</v>
       </c>
       <c r="G3">
-        <v>-10.55891080972194</v>
+        <v>-6.708659807438323</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.40420518103172</v>
       </c>
       <c r="E4">
-        <v>-18.86025402248922</v>
+        <v>-14.98855818557331</v>
       </c>
       <c r="F4">
-        <v>-1.570733020720471</v>
+        <v>-0.8520663130737044</v>
       </c>
       <c r="G4">
-        <v>-9.817495829814492</v>
+        <v>-4.883959373344879</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.88477870920667</v>
       </c>
       <c r="E5">
-        <v>-19.02491386588212</v>
+        <v>-15.70326006735988</v>
       </c>
       <c r="F5">
-        <v>-1.808456241241068</v>
+        <v>-1.155312566788339</v>
       </c>
       <c r="G5">
-        <v>-9.473561467175056</v>
+        <v>-6.797564505591478</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.37622001443988</v>
       </c>
       <c r="E6">
-        <v>-19.3584722043391</v>
+        <v>-16.31846684672392</v>
       </c>
       <c r="F6">
-        <v>-1.680016218702199</v>
+        <v>-0.8436807498551651</v>
       </c>
       <c r="G6">
-        <v>-9.044879714098283</v>
+        <v>-6.338193487269217</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.87809814588519</v>
       </c>
       <c r="E7">
-        <v>-20.17805807261732</v>
+        <v>-17.527035046839</v>
       </c>
       <c r="F7">
-        <v>-1.740966663832784</v>
+        <v>-1.222662978472953</v>
       </c>
       <c r="G7">
-        <v>-8.816775753728804</v>
+        <v>-5.645708083256207</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.40378489056595</v>
       </c>
       <c r="E8">
-        <v>-19.76486651873545</v>
+        <v>-18.65734668762753</v>
       </c>
       <c r="F8">
-        <v>-1.28832766249287</v>
+        <v>-0.5853452632507085</v>
       </c>
       <c r="G8">
-        <v>-8.790985352271569</v>
+        <v>-5.109750072514948</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.95890849185959</v>
       </c>
       <c r="E9">
-        <v>-20.98269091972221</v>
+        <v>-19.63927834908073</v>
       </c>
       <c r="F9">
-        <v>-1.758053398250329</v>
+        <v>-1.062764047077967</v>
       </c>
       <c r="G9">
-        <v>-8.972840494760673</v>
+        <v>-6.316104303731035</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.51434313355884</v>
       </c>
       <c r="E10">
-        <v>-22.10910354439013</v>
+        <v>-19.75398459569502</v>
       </c>
       <c r="F10">
-        <v>-1.20901231204222</v>
+        <v>-0.848114172194948</v>
       </c>
       <c r="G10">
-        <v>-8.537107396552653</v>
+        <v>-5.120814351613395</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.07576714039379</v>
       </c>
       <c r="E11">
-        <v>-21.98952013126959</v>
+        <v>-19.72660997031865</v>
       </c>
       <c r="F11">
-        <v>-1.134075711682768</v>
+        <v>-0.8279591649174332</v>
       </c>
       <c r="G11">
-        <v>-8.605645552486335</v>
+        <v>-6.133245107444741</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-15.63457044766794</v>
       </c>
       <c r="E12">
-        <v>-22.43549330849298</v>
+        <v>-22.59384045911919</v>
       </c>
       <c r="F12">
-        <v>-0.9756272516100842</v>
+        <v>0.08159901213266035</v>
       </c>
       <c r="G12">
-        <v>-7.882155885958131</v>
+        <v>-6.112904814997743</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-15.16555387290328</v>
       </c>
       <c r="E13">
-        <v>-23.31629961688089</v>
+        <v>-22.01192249218553</v>
       </c>
       <c r="F13">
-        <v>-0.650746526436535</v>
+        <v>-0.01285972280856728</v>
       </c>
       <c r="G13">
-        <v>-7.619211915070469</v>
+        <v>-6.163366721360443</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.6914711476793</v>
       </c>
       <c r="E14">
-        <v>-23.97689981969782</v>
+        <v>-21.33991053486927</v>
       </c>
       <c r="F14">
-        <v>-0.4672863410037228</v>
+        <v>0.6846852728016181</v>
       </c>
       <c r="G14">
-        <v>-7.460036576000246</v>
+        <v>-4.644725509445765</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.22095579130287</v>
       </c>
       <c r="E15">
-        <v>-24.68768909994176</v>
+        <v>-23.74824358162852</v>
       </c>
       <c r="F15">
-        <v>-0.2425303838065498</v>
+        <v>-0.09185449507433373</v>
       </c>
       <c r="G15">
-        <v>-7.179479007781485</v>
+        <v>-5.047902327340974</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.75268931712433</v>
       </c>
       <c r="E16">
-        <v>-25.00034400237934</v>
+        <v>-22.71039885160261</v>
       </c>
       <c r="F16">
-        <v>-0.2721022717190894</v>
+        <v>1.067383557588364</v>
       </c>
       <c r="G16">
-        <v>-6.741849363512106</v>
+        <v>-4.264730521868032</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.322750456596</v>
       </c>
       <c r="E17">
-        <v>-26.13450484607439</v>
+        <v>-23.89115316436258</v>
       </c>
       <c r="F17">
-        <v>0.1656700198427822</v>
+        <v>1.334248743339448</v>
       </c>
       <c r="G17">
-        <v>-6.509053256312622</v>
+        <v>-5.070742910616269</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.94166330436245</v>
       </c>
       <c r="E18">
-        <v>-27.09077817380013</v>
+        <v>-25.91010084509829</v>
       </c>
       <c r="F18">
-        <v>0.4690156776457527</v>
+        <v>1.0287203374301</v>
       </c>
       <c r="G18">
-        <v>-6.412923308285571</v>
+        <v>-4.172170542897655</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-12.60585897423312</v>
       </c>
       <c r="E19">
-        <v>-27.28498631009308</v>
+        <v>-26.60878098584572</v>
       </c>
       <c r="F19">
-        <v>0.5743036596437783</v>
+        <v>1.494663747626377</v>
       </c>
       <c r="G19">
-        <v>-5.754959636299478</v>
+        <v>-5.693187359221373</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.3361271874246</v>
       </c>
       <c r="E20">
-        <v>-28.9750354521257</v>
+        <v>-26.71939349195707</v>
       </c>
       <c r="F20">
-        <v>0.7181074124023696</v>
+        <v>2.094617122777947</v>
       </c>
       <c r="G20">
-        <v>-5.331239090220585</v>
+        <v>-3.694608432249834</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.12370386159025</v>
       </c>
       <c r="E21">
-        <v>-28.99951185413715</v>
+        <v>-26.69037050204192</v>
       </c>
       <c r="F21">
-        <v>1.354353220205392</v>
+        <v>2.083150861188396</v>
       </c>
       <c r="G21">
-        <v>-5.874599536799952</v>
+        <v>-4.086599565848896</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.95483649730384</v>
       </c>
       <c r="E22">
-        <v>-29.87664330586784</v>
+        <v>-28.20354197780893</v>
       </c>
       <c r="F22">
-        <v>1.419394971938403</v>
+        <v>2.451191184782606</v>
       </c>
       <c r="G22">
-        <v>-6.069648471179583</v>
+        <v>-3.123072136139515</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.83549273738647</v>
       </c>
       <c r="E23">
-        <v>-29.74580437060123</v>
+        <v>-29.1009089156429</v>
       </c>
       <c r="F23">
-        <v>1.500584917821588</v>
+        <v>2.879203651604693</v>
       </c>
       <c r="G23">
-        <v>-5.828882276812209</v>
+        <v>-3.241809700711141</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.74862330767009</v>
       </c>
       <c r="E24">
-        <v>-30.79399892797166</v>
+        <v>-30.10707017727414</v>
       </c>
       <c r="F24">
-        <v>1.909486948661091</v>
+        <v>3.300126950193623</v>
       </c>
       <c r="G24">
-        <v>-5.630286341926817</v>
+        <v>-3.046389988295292</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-11.68118543296483</v>
       </c>
       <c r="E25">
-        <v>-31.22526362161814</v>
+        <v>-28.83483842532223</v>
       </c>
       <c r="F25">
-        <v>2.176040668268722</v>
+        <v>2.820218922320952</v>
       </c>
       <c r="G25">
-        <v>-5.660949357399828</v>
+        <v>-2.482889403784054</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.63456482977509</v>
       </c>
       <c r="E26">
-        <v>-31.61272212195142</v>
+        <v>-29.93590065249521</v>
       </c>
       <c r="F26">
-        <v>1.942094803104891</v>
+        <v>2.963876054049248</v>
       </c>
       <c r="G26">
-        <v>-4.970905182227045</v>
+        <v>-2.962561339894599</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.58970946551365</v>
       </c>
       <c r="E27">
-        <v>-31.76609700811721</v>
+        <v>-30.33119114862476</v>
       </c>
       <c r="F27">
-        <v>2.144675364929121</v>
+        <v>2.909637869983547</v>
       </c>
       <c r="G27">
-        <v>-5.532263129059966</v>
+        <v>-3.001391315829068</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.53727031734637</v>
       </c>
       <c r="E28">
-        <v>-32.0197821220269</v>
+        <v>-30.27954616680428</v>
       </c>
       <c r="F28">
-        <v>2.171408437752267</v>
+        <v>3.364631919849621</v>
       </c>
       <c r="G28">
-        <v>-5.354630918717866</v>
+        <v>-2.752592691084172</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.47574947123966</v>
       </c>
       <c r="E29">
-        <v>-32.76624219202926</v>
+        <v>-30.74546727203146</v>
       </c>
       <c r="F29">
-        <v>2.236143693546243</v>
+        <v>3.168994733595656</v>
       </c>
       <c r="G29">
-        <v>-5.303243707875403</v>
+        <v>-2.99800837640128</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.38733188092831</v>
       </c>
       <c r="E30">
-        <v>-31.26421302655812</v>
+        <v>-30.47814239441066</v>
       </c>
       <c r="F30">
-        <v>2.042438260075607</v>
+        <v>3.14011950266887</v>
       </c>
       <c r="G30">
-        <v>-5.761134895274354</v>
+        <v>-3.797796287851251</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.27022759039331</v>
       </c>
       <c r="E31">
-        <v>-31.30117216717172</v>
+        <v>-31.01664135255878</v>
       </c>
       <c r="F31">
-        <v>1.84118142936105</v>
+        <v>3.021018494229163</v>
       </c>
       <c r="G31">
-        <v>-5.094587547688754</v>
+        <v>-2.498439112754263</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.12721374442704</v>
       </c>
       <c r="E32">
-        <v>-31.78426524583599</v>
+        <v>-30.17715963372786</v>
       </c>
       <c r="F32">
-        <v>1.970676791971085</v>
+        <v>2.954807087723399</v>
       </c>
       <c r="G32">
-        <v>-5.053001345644351</v>
+        <v>-2.896470975244263</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.94771528849027</v>
       </c>
       <c r="E33">
-        <v>-31.47079748231403</v>
+        <v>-29.4670677384811</v>
       </c>
       <c r="F33">
-        <v>1.909283170280003</v>
+        <v>2.550210910643647</v>
       </c>
       <c r="G33">
-        <v>-5.435198032888472</v>
+        <v>-2.927721329376415</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.74244625685223</v>
       </c>
       <c r="E34">
-        <v>-30.7359235130603</v>
+        <v>-28.30634739473107</v>
       </c>
       <c r="F34">
-        <v>1.669419448390572</v>
+        <v>3.013187108803097</v>
       </c>
       <c r="G34">
-        <v>-5.311515667426763</v>
+        <v>-2.854806023882434</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.52237959491507</v>
       </c>
       <c r="E35">
-        <v>-31.27792298161634</v>
+        <v>-29.52190076600298</v>
       </c>
       <c r="F35">
-        <v>1.653385568941985</v>
+        <v>2.582523866292051</v>
       </c>
       <c r="G35">
-        <v>-5.046068124489245</v>
+        <v>-2.874831319059725</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.28530959983871</v>
       </c>
       <c r="E36">
-        <v>-30.50848543449906</v>
+        <v>-29.19853828677427</v>
       </c>
       <c r="F36">
-        <v>1.693120696519472</v>
+        <v>2.515464211565819</v>
       </c>
       <c r="G36">
-        <v>-4.585437117088158</v>
+        <v>-2.177063148336009</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.05311343025135</v>
       </c>
       <c r="E37">
-        <v>-30.17655734668484</v>
+        <v>-27.80864545891805</v>
       </c>
       <c r="F37">
-        <v>1.611955601658371</v>
+        <v>2.973690551037616</v>
       </c>
       <c r="G37">
-        <v>-4.421300571020055</v>
+        <v>-1.381494887811484</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.839909013986848</v>
       </c>
       <c r="E38">
-        <v>-29.484717465926</v>
+        <v>-26.27620079777439</v>
       </c>
       <c r="F38">
-        <v>1.772445159011552</v>
+        <v>2.261306181773681</v>
       </c>
       <c r="G38">
-        <v>-4.42800738788756</v>
+        <v>-1.444966837657383</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.643989021089457</v>
       </c>
       <c r="E39">
-        <v>-29.80187140729019</v>
+        <v>-28.31889579620632</v>
       </c>
       <c r="F39">
-        <v>1.507001451723673</v>
+        <v>2.666288378063137</v>
       </c>
       <c r="G39">
-        <v>-4.175107236193359</v>
+        <v>-2.350659456159991</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.48573269623378</v>
       </c>
       <c r="E40">
-        <v>-28.50478059727317</v>
+        <v>-26.91268234802647</v>
       </c>
       <c r="F40">
-        <v>1.482569583545505</v>
+        <v>2.221935535853426</v>
       </c>
       <c r="G40">
-        <v>-4.679129117496542</v>
+        <v>-2.046257250868746</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.369696229056585</v>
       </c>
       <c r="E41">
-        <v>-28.69809662418661</v>
+        <v>-26.12976353378836</v>
       </c>
       <c r="F41">
-        <v>1.640960057899993</v>
+        <v>2.157037920048501</v>
       </c>
       <c r="G41">
-        <v>-3.665366185712062</v>
+        <v>-3.470947245871844</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.285674834032861</v>
       </c>
       <c r="E42">
-        <v>-28.4593962307683</v>
+        <v>-24.36824601496669</v>
       </c>
       <c r="F42">
-        <v>1.300048766747467</v>
+        <v>2.495197374688927</v>
       </c>
       <c r="G42">
-        <v>-4.4503426630427</v>
+        <v>-2.131539480420273</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.24599138223866</v>
       </c>
       <c r="E43">
-        <v>-27.25825925649981</v>
+        <v>-24.5427734032223</v>
       </c>
       <c r="F43">
-        <v>1.359132900119545</v>
+        <v>2.901586138828336</v>
       </c>
       <c r="G43">
-        <v>-4.076391685577464</v>
+        <v>-2.407106310647119</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.246750377960154</v>
       </c>
       <c r="E44">
-        <v>-27.16213333873899</v>
+        <v>-24.72617207205894</v>
       </c>
       <c r="F44">
-        <v>1.509393776782958</v>
+        <v>2.498393216128927</v>
       </c>
       <c r="G44">
-        <v>-3.974595067917251</v>
+        <v>-1.310850187636639</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.274952565370272</v>
       </c>
       <c r="E45">
-        <v>-26.97494433715793</v>
+        <v>-24.11281743856404</v>
       </c>
       <c r="F45">
-        <v>1.313933861153193</v>
+        <v>1.996989054153609</v>
       </c>
       <c r="G45">
-        <v>-3.707720193601375</v>
+        <v>-2.037539045185301</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.339653191173863</v>
       </c>
       <c r="E46">
-        <v>-26.25334558945768</v>
+        <v>-22.50217508825592</v>
       </c>
       <c r="F46">
-        <v>1.252710883147087</v>
+        <v>2.68550484507328</v>
       </c>
       <c r="G46">
-        <v>-4.03085817399705</v>
+        <v>-1.806938075209086</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.432774849495752</v>
       </c>
       <c r="E47">
-        <v>-26.14314970295503</v>
+        <v>-23.71442946621325</v>
       </c>
       <c r="F47">
-        <v>1.209267983074669</v>
+        <v>2.147591218186976</v>
       </c>
       <c r="G47">
-        <v>-3.73504948796999</v>
+        <v>-0.5480974239281208</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.543757417813014</v>
       </c>
       <c r="E48">
-        <v>-24.76577810573003</v>
+        <v>-22.21429546711431</v>
       </c>
       <c r="F48">
-        <v>1.105864536918013</v>
+        <v>1.960023987171084</v>
       </c>
       <c r="G48">
-        <v>-4.053528133751254</v>
+        <v>-1.594807101390985</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.681599019942549</v>
       </c>
       <c r="E49">
-        <v>-24.72186096480364</v>
+        <v>-22.69574018123978</v>
       </c>
       <c r="F49">
-        <v>1.117034242977361</v>
+        <v>2.197258470924028</v>
       </c>
       <c r="G49">
-        <v>-3.860139497480701</v>
+        <v>-2.194981899272137</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.839685561795516</v>
       </c>
       <c r="E50">
-        <v>-23.85994292150172</v>
+        <v>-21.38013696947941</v>
       </c>
       <c r="F50">
-        <v>1.340993310733041</v>
+        <v>2.339800620128156</v>
       </c>
       <c r="G50">
-        <v>-3.768147169840109</v>
+        <v>-2.105775328735513</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.01218679316246</v>
       </c>
       <c r="E51">
-        <v>-24.02326686506236</v>
+        <v>-21.76702261785072</v>
       </c>
       <c r="F51">
-        <v>1.328014450265979</v>
+        <v>2.477190324086871</v>
       </c>
       <c r="G51">
-        <v>-4.12120660963636</v>
+        <v>-1.721206318303914</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.20666178363249</v>
       </c>
       <c r="E52">
-        <v>-22.67679304599169</v>
+        <v>-19.91496731819369</v>
       </c>
       <c r="F52">
-        <v>1.232697526695451</v>
+        <v>2.841435068241453</v>
       </c>
       <c r="G52">
-        <v>-3.643598561886706</v>
+        <v>-2.713493654981828</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.41341604313407</v>
       </c>
       <c r="E53">
-        <v>-22.36344075855693</v>
+        <v>-19.91107735902111</v>
       </c>
       <c r="F53">
-        <v>1.188234077982784</v>
+        <v>2.457476836635049</v>
       </c>
       <c r="G53">
-        <v>-4.305591573947797</v>
+        <v>-2.161054068347478</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.62793355524734</v>
       </c>
       <c r="E54">
-        <v>-22.41744733957241</v>
+        <v>-18.78055740842822</v>
       </c>
       <c r="F54">
-        <v>1.20886870998652</v>
+        <v>2.265555706550042</v>
       </c>
       <c r="G54">
-        <v>-4.97607638740473</v>
+        <v>-1.813480830998619</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.85372151773364</v>
       </c>
       <c r="E55">
-        <v>-22.12291086163952</v>
+        <v>-19.76522426818206</v>
       </c>
       <c r="F55">
-        <v>0.9885743396208251</v>
+        <v>1.909750369495182</v>
       </c>
       <c r="G55">
-        <v>-4.618777609353676</v>
+        <v>-3.416738184488258</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.07585392497655</v>
       </c>
       <c r="E56">
-        <v>-21.87509465004377</v>
+        <v>-18.35147996772745</v>
       </c>
       <c r="F56">
-        <v>1.248769511044566</v>
+        <v>1.984714305978926</v>
       </c>
       <c r="G56">
-        <v>-4.975666234709799</v>
+        <v>-2.032252997253036</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.28986605766727</v>
       </c>
       <c r="E57">
-        <v>-21.69514214992697</v>
+        <v>-18.96997441922106</v>
       </c>
       <c r="F57">
-        <v>0.8829939439296113</v>
+        <v>1.984233852885302</v>
       </c>
       <c r="G57">
-        <v>-4.87124792102359</v>
+        <v>-3.151779543563097</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.49485568681603</v>
       </c>
       <c r="E58">
-        <v>-20.4113695819665</v>
+        <v>-18.75965397240882</v>
       </c>
       <c r="F58">
-        <v>1.260191040794366</v>
+        <v>1.457140361014365</v>
       </c>
       <c r="G58">
-        <v>-5.158932302469465</v>
+        <v>-3.008019383379146</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.67286795930588</v>
       </c>
       <c r="E59">
-        <v>-20.83435622512696</v>
+        <v>-15.62963160846917</v>
       </c>
       <c r="F59">
-        <v>1.207380962131092</v>
+        <v>2.784567646039267</v>
       </c>
       <c r="G59">
-        <v>-5.217761323808749</v>
+        <v>-3.082325926814331</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.82327844080338</v>
       </c>
       <c r="E60">
-        <v>-20.16176915161173</v>
+        <v>-18.32497933783456</v>
       </c>
       <c r="F60">
-        <v>1.055069047778347</v>
+        <v>2.016644555887236</v>
       </c>
       <c r="G60">
-        <v>-5.718459327672216</v>
+        <v>-3.532808115932055</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.94507850014136</v>
       </c>
       <c r="E61">
-        <v>-19.76728019538154</v>
+        <v>-18.4746635176841</v>
       </c>
       <c r="F61">
-        <v>1.003276204285711</v>
+        <v>1.966316265962749</v>
       </c>
       <c r="G61">
-        <v>-5.847736175892778</v>
+        <v>-2.627148309645041</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.02140631958843</v>
       </c>
       <c r="E62">
-        <v>-18.8609514074864</v>
+        <v>-16.2601853862452</v>
       </c>
       <c r="F62">
-        <v>0.8709362280144617</v>
+        <v>1.468179185024072</v>
       </c>
       <c r="G62">
-        <v>-5.754972761185717</v>
+        <v>-3.33719153022264</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.05867772086775</v>
       </c>
       <c r="E63">
-        <v>-19.46650800874009</v>
+        <v>-16.48261044407995</v>
       </c>
       <c r="F63">
-        <v>0.9314766312806607</v>
+        <v>1.495324784813811</v>
       </c>
       <c r="G63">
-        <v>-5.845862598382335</v>
+        <v>-5.122369650632573</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.05716603540999</v>
       </c>
       <c r="E64">
-        <v>-18.41391856734521</v>
+        <v>-15.87326803855584</v>
       </c>
       <c r="F64">
-        <v>0.7034535930468464</v>
+        <v>1.85779019578718</v>
       </c>
       <c r="G64">
-        <v>-5.96058722898676</v>
+        <v>-4.20683008623007</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.00382793743059</v>
       </c>
       <c r="E65">
-        <v>-18.6985376872013</v>
+        <v>-15.31413735282878</v>
       </c>
       <c r="F65">
-        <v>0.5462394004043338</v>
+        <v>1.836343763728701</v>
       </c>
       <c r="G65">
-        <v>-6.143790953536796</v>
+        <v>-5.564983470450748</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.91218979282816</v>
       </c>
       <c r="E66">
-        <v>-18.84871999919168</v>
+        <v>-16.54731780917555</v>
       </c>
       <c r="F66">
-        <v>0.7720987429820358</v>
+        <v>1.509025981656115</v>
       </c>
       <c r="G66">
-        <v>-6.352470082274361</v>
+        <v>-4.378641409525714</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.78380907223653</v>
       </c>
       <c r="E67">
-        <v>-18.75436018629385</v>
+        <v>-16.13878152657357</v>
       </c>
       <c r="F67">
-        <v>0.6520550524379427</v>
+        <v>1.012109914269165</v>
       </c>
       <c r="G67">
-        <v>-7.038622728677643</v>
+        <v>-5.187633147449928</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.61096865795773</v>
       </c>
       <c r="E68">
-        <v>-18.05797598186831</v>
+        <v>-13.5612918617318</v>
       </c>
       <c r="F68">
-        <v>0.3813793766339819</v>
+        <v>1.369798958797991</v>
       </c>
       <c r="G68">
-        <v>-6.902120630583183</v>
+        <v>-4.203315897939905</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.41062341468911</v>
       </c>
       <c r="E69">
-        <v>-18.14463286047909</v>
+        <v>-16.1582811356506</v>
       </c>
       <c r="F69">
-        <v>0.1081887773951217</v>
+        <v>1.652857070538999</v>
       </c>
       <c r="G69">
-        <v>-7.277216754372666</v>
+        <v>-5.159985574590046</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.18473480052639</v>
       </c>
       <c r="E70">
-        <v>-17.57340209220354</v>
+        <v>-14.33863159599246</v>
       </c>
       <c r="F70">
-        <v>0.3381758747409736</v>
+        <v>0.9349126992674731</v>
       </c>
       <c r="G70">
-        <v>-6.507753892575082</v>
+        <v>-4.987504882096276</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.93120580089043</v>
       </c>
       <c r="E71">
-        <v>-18.08354374611562</v>
+        <v>-15.0147644646557</v>
       </c>
       <c r="F71">
-        <v>0.1886348493505929</v>
+        <v>1.062166499685533</v>
       </c>
       <c r="G71">
-        <v>-7.266047476184315</v>
+        <v>-4.903846857216673</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.66813156123732</v>
       </c>
       <c r="E72">
-        <v>-17.29370542359379</v>
+        <v>-13.76241950630847</v>
       </c>
       <c r="F72">
-        <v>0.1794242321988652</v>
+        <v>1.227772054118405</v>
       </c>
       <c r="G72">
-        <v>-6.976020302544997</v>
+        <v>-5.698568562578862</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.39694514260068</v>
       </c>
       <c r="E73">
-        <v>-18.06648951300273</v>
+        <v>-15.95612552747418</v>
       </c>
       <c r="F73">
-        <v>-0.1240986962283045</v>
+        <v>0.9232310621531944</v>
       </c>
       <c r="G73">
-        <v>-7.242160183231558</v>
+        <v>-4.993502955106941</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.11998056136627</v>
       </c>
       <c r="E74">
-        <v>-18.26046216864728</v>
+        <v>-14.58225444065711</v>
       </c>
       <c r="F74">
-        <v>0.01675109837190385</v>
+        <v>1.146734527837335</v>
       </c>
       <c r="G74">
-        <v>-6.750941628453328</v>
+        <v>-4.498008968636753</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.853776149242407</v>
       </c>
       <c r="E75">
-        <v>-18.3725871850772</v>
+        <v>-16.13924343092235</v>
       </c>
       <c r="F75">
-        <v>-0.3184287187206517</v>
+        <v>1.029555331772122</v>
       </c>
       <c r="G75">
-        <v>-7.383282241281716</v>
+        <v>-4.958387321977763</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.597401860257664</v>
       </c>
       <c r="E76">
-        <v>-18.80160122714187</v>
+        <v>-15.53535783657748</v>
       </c>
       <c r="F76">
-        <v>-0.3564888874096778</v>
+        <v>0.3174410102814992</v>
       </c>
       <c r="G76">
-        <v>-5.967333420512978</v>
+        <v>-5.381244906786523</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.355541708033675</v>
       </c>
       <c r="E77">
-        <v>-18.59169287146432</v>
+        <v>-15.33236898918366</v>
       </c>
       <c r="F77">
-        <v>-0.4150420372765609</v>
+        <v>0.4627880115115061</v>
       </c>
       <c r="G77">
-        <v>-6.125409550360787</v>
+        <v>-4.056343421849257</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.140713896406256</v>
       </c>
       <c r="E78">
-        <v>-19.36876089728453</v>
+        <v>-15.35230786023943</v>
       </c>
       <c r="F78">
-        <v>-0.5421077982941854</v>
+        <v>0.01799613457831151</v>
       </c>
       <c r="G78">
-        <v>-6.82579613588894</v>
+        <v>-4.795937323791215</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.948393528725996</v>
       </c>
       <c r="E79">
-        <v>-19.42891261752841</v>
+        <v>-17.1960081253523</v>
       </c>
       <c r="F79">
-        <v>-0.3613986210060705</v>
+        <v>0.4475924398745519</v>
       </c>
       <c r="G79">
-        <v>-5.831969906299646</v>
+        <v>-4.935628769241455</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.783085760892096</v>
       </c>
       <c r="E80">
-        <v>-19.87598621393567</v>
+        <v>-17.85832461981814</v>
       </c>
       <c r="F80">
-        <v>-0.5671385761045781</v>
+        <v>0.1643206093436218</v>
       </c>
       <c r="G80">
-        <v>-5.793766643683031</v>
+        <v>-3.610668222316119</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.65188469715352</v>
       </c>
       <c r="E81">
-        <v>-20.26504552983066</v>
+        <v>-17.08940784721174</v>
       </c>
       <c r="F81">
-        <v>-0.7540928152423985</v>
+        <v>0.3414106494489057</v>
       </c>
       <c r="G81">
-        <v>-5.644658092357185</v>
+        <v>-4.323585792979792</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.54517043240997</v>
       </c>
       <c r="E82">
-        <v>-21.01330340401406</v>
+        <v>-18.34115051851595</v>
       </c>
       <c r="F82">
-        <v>-0.6207455442093452</v>
+        <v>-0.27430987084755</v>
       </c>
       <c r="G82">
-        <v>-5.565226280846147</v>
+        <v>-3.183695985671816</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.466261027638534</v>
       </c>
       <c r="E83">
-        <v>-21.56911924676751</v>
+        <v>-20.09077173611947</v>
       </c>
       <c r="F83">
-        <v>-0.6793318287723403</v>
+        <v>0.2013121840830365</v>
       </c>
       <c r="G83">
-        <v>-5.744909254662899</v>
+        <v>-4.092203892272428</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.416635120759194</v>
       </c>
       <c r="E84">
-        <v>-22.88975812162441</v>
+        <v>-20.53022843924583</v>
       </c>
       <c r="F84">
-        <v>-0.7117640693267465</v>
+        <v>0.3026463684675</v>
       </c>
       <c r="G84">
-        <v>-5.33126862121462</v>
+        <v>-3.691179555720214</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.38235496094158</v>
       </c>
       <c r="E85">
-        <v>-23.92010369869362</v>
+        <v>-20.06810219523707</v>
       </c>
       <c r="F85">
-        <v>-0.6906340736161368</v>
+        <v>-0.05595885040882276</v>
       </c>
       <c r="G85">
-        <v>-5.238282083441517</v>
+        <v>-3.876834352775155</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.366322952095398</v>
       </c>
       <c r="E86">
-        <v>-24.55485084340076</v>
+        <v>-21.77355267736978</v>
       </c>
       <c r="F86">
-        <v>-0.8879313081453118</v>
+        <v>-0.05551236037871382</v>
       </c>
       <c r="G86">
-        <v>-4.916308936699444</v>
+        <v>-2.887070275476454</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.366030732830337</v>
       </c>
       <c r="E87">
-        <v>-25.7277980669715</v>
+        <v>-24.04709116681671</v>
       </c>
       <c r="F87">
-        <v>-0.6742953549633193</v>
+        <v>-0.2862077118539593</v>
       </c>
       <c r="G87">
-        <v>-4.770179734549574</v>
+        <v>-2.592285330575941</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.366060131064517</v>
       </c>
       <c r="E88">
-        <v>-27.33846305964966</v>
+        <v>-24.024240486974</v>
       </c>
       <c r="F88">
-        <v>-1.106655093915299</v>
+        <v>-0.6899283045889516</v>
       </c>
       <c r="G88">
-        <v>-4.311770114144231</v>
+        <v>-3.006247523737046</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.37155651539137</v>
       </c>
       <c r="E89">
-        <v>-28.48363715213136</v>
+        <v>-26.75897688325812</v>
       </c>
       <c r="F89">
-        <v>-0.7559856347577953</v>
+        <v>-0.4700439760876424</v>
       </c>
       <c r="G89">
-        <v>-4.93588798574465</v>
+        <v>-2.516991139451363</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.380220001479541</v>
       </c>
       <c r="E90">
-        <v>-29.91945776337336</v>
+        <v>-27.78047835059035</v>
       </c>
       <c r="F90">
-        <v>-1.0736628769966</v>
+        <v>-0.3377860081892706</v>
       </c>
       <c r="G90">
-        <v>-4.289989365432636</v>
+        <v>-2.380948412375226</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.379980006958659</v>
       </c>
       <c r="E91">
-        <v>-31.48927139202832</v>
+        <v>-29.6953118854157</v>
       </c>
       <c r="F91">
-        <v>-1.197999167422</v>
+        <v>-0.2432759144690693</v>
       </c>
       <c r="G91">
-        <v>-4.705316546762471</v>
+        <v>-2.673075567812589</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.379451481174478</v>
       </c>
       <c r="E92">
-        <v>-32.60964303237002</v>
+        <v>-32.83968271924866</v>
       </c>
       <c r="F92">
-        <v>-1.246971419908104</v>
+        <v>-0.7227714153751464</v>
       </c>
       <c r="G92">
-        <v>-4.219498882671086</v>
+        <v>-2.682538610790027</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.376890739058956</v>
       </c>
       <c r="E93">
-        <v>-34.45132586231247</v>
+        <v>-31.94139650119114</v>
       </c>
       <c r="F93">
-        <v>-1.170444354135278</v>
+        <v>-0.9243322569265305</v>
       </c>
       <c r="G93">
-        <v>-4.130981368661946</v>
+        <v>-1.952233847082858</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.362555740894178</v>
       </c>
       <c r="E94">
-        <v>-36.35827985236448</v>
+        <v>-34.60078814693563</v>
       </c>
       <c r="F94">
-        <v>-1.15273551579823</v>
+        <v>-1.434650480523374</v>
       </c>
       <c r="G94">
-        <v>-4.740409211340732</v>
+        <v>-1.775517097555843</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.345548338952879</v>
       </c>
       <c r="E95">
-        <v>-38.2098619264877</v>
+        <v>-36.08316373521349</v>
       </c>
       <c r="F95">
-        <v>-1.126627860364198</v>
+        <v>-1.085800116182418</v>
       </c>
       <c r="G95">
-        <v>-4.771016446047232</v>
+        <v>-3.380979431933429</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.321571378032608</v>
       </c>
       <c r="E96">
-        <v>-40.84762331613456</v>
+        <v>-38.08686857243937</v>
       </c>
       <c r="F96">
-        <v>-1.359164672575867</v>
+        <v>-1.501809539337941</v>
       </c>
       <c r="G96">
-        <v>-4.626767383850924</v>
+        <v>-2.843164249789524</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.28290981692321</v>
       </c>
       <c r="E97">
-        <v>-42.31332959159018</v>
+        <v>-41.18450102603916</v>
       </c>
       <c r="F97">
-        <v>-1.39359327857102</v>
+        <v>-1.464761635615136</v>
       </c>
       <c r="G97">
-        <v>-4.654391988159889</v>
+        <v>-2.577542802109356</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.236808349272339</v>
       </c>
       <c r="E98">
-        <v>-43.98181866887228</v>
+        <v>-41.86912931194079</v>
       </c>
       <c r="F98">
-        <v>-1.525941538516297</v>
+        <v>-1.117524930974834</v>
       </c>
       <c r="G98">
-        <v>-5.589113573798905</v>
+        <v>-3.260748911552256</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.177950298502351</v>
       </c>
       <c r="E99">
-        <v>-45.59167080046605</v>
+        <v>-43.67481530199628</v>
       </c>
       <c r="F99">
-        <v>-1.663988966192834</v>
+        <v>-1.22241943845653</v>
       </c>
       <c r="G99">
-        <v>-5.941815360445177</v>
+        <v>-3.318176851285658</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.103002909339551</v>
       </c>
       <c r="E100">
-        <v>-48.56359168349442</v>
+        <v>-44.92146570427886</v>
       </c>
       <c r="F100">
-        <v>-1.596387559185172</v>
+        <v>-2.086143218742324</v>
       </c>
       <c r="G100">
-        <v>-6.102017721863506</v>
+        <v>-4.051749711666035</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.017956204124527</v>
       </c>
       <c r="E101">
-        <v>-49.61367687876305</v>
+        <v>-48.33807254579393</v>
       </c>
       <c r="F101">
-        <v>-1.785132728647845</v>
+        <v>-1.893107934500552</v>
       </c>
       <c r="G101">
-        <v>-6.577742348438038</v>
+        <v>-3.802163593746872</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.91865490671065</v>
       </c>
       <c r="E102">
-        <v>-52.37093677264281</v>
+        <v>-50.60184424892482</v>
       </c>
       <c r="F102">
-        <v>-1.838800995940419</v>
+        <v>-2.186859441044299</v>
       </c>
       <c r="G102">
-        <v>-6.341133461786479</v>
+        <v>-4.613609685397551</v>
       </c>
     </row>
   </sheetData>
